--- a/Corte_2.xlsx
+++ b/Corte_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2682" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{877296BA-2D6D-46D7-9243-E1B51B61D981}"/>
+  <xr:revisionPtr revIDLastSave="2698" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0ECA88A-A865-43F9-B6CC-24EF1CADB1E8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4903,8 +4903,8 @@
         <v>4.5</v>
       </c>
       <c r="F8" s="5">
-        <f>AVERAGE(E8:E8)*0.5</f>
-        <v>2.25</v>
+        <f>AVERAGE(E8:E8)*0.48</f>
+        <v>2.16</v>
       </c>
       <c r="G8" s="1">
         <v>2.1</v>
@@ -4913,18 +4913,20 @@
         <f>G8*0.5</f>
         <v>1.05</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="6">
+        <v>5</v>
+      </c>
       <c r="J8" s="6">
-        <f>(SUM(I8:I8)/5)*0.01</f>
-        <v>0</v>
+        <f>(SUM(I8:I8)/10)*0.1</f>
+        <v>0.05</v>
       </c>
       <c r="K8" s="6">
-        <f>H8+F8+J8</f>
-        <v>3.3</v>
+        <f>H8+F8</f>
+        <v>3.21</v>
       </c>
       <c r="L8" s="6">
-        <f>INT(K8*10)/10+IF(MOD(K8*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.3</v>
+        <f>INT(K8*10)/10+IF(MOD(K8*10,1)&gt;=0.5,0.1,0)+J8</f>
+        <v>3.25</v>
       </c>
       <c r="M8" s="1" t="str">
         <f>IF(K8&lt;3,3-K8,"No aplica")</f>
@@ -4944,8 +4946,8 @@
         <v>4.3</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" ref="F9:F39" si="0">AVERAGE(E9:E9)*0.5</f>
-        <v>2.15</v>
+        <f t="shared" ref="F9:F39" si="0">AVERAGE(E9:E9)*0.48</f>
+        <v>2.0640000000000001</v>
       </c>
       <c r="G9" s="1">
         <v>5</v>
@@ -4956,16 +4958,16 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6">
-        <f t="shared" ref="J9:J39" si="1">(SUM(I9:I9)/5)*0.01</f>
+        <f t="shared" ref="J9:J39" si="1">(SUM(I9:I9)/10)*0.1</f>
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" ref="K9:K39" si="2">H9+F9+J9</f>
-        <v>4.6500000000000004</v>
+        <f t="shared" ref="K9:K39" si="2">H9+F9</f>
+        <v>4.5640000000000001</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" ref="L9:L39" si="3">INT(K9*10)/10+IF(MOD(K9*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.6999999999999993</v>
+        <f t="shared" ref="L9:L39" si="3">INT(K9*10)/10+IF(MOD(K9*10,1)&gt;=0.5,0.1,0)+J9</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="M9" s="1" t="str">
         <f>IF(K9&lt;3,3-K9,"No aplica")</f>
@@ -4986,7 +4988,7 @@
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>2.35</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -5000,15 +5002,15 @@
       </c>
       <c r="J10" s="6">
         <f t="shared" si="1"/>
-        <v>1.3999999999999999E-2</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="K10" s="6">
         <f t="shared" si="2"/>
-        <v>4.8639999999999999</v>
+        <v>4.7560000000000002</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="3"/>
-        <v>4.8999999999999995</v>
+        <v>4.87</v>
       </c>
       <c r="M10" s="1" t="str">
         <f>IF(K10&lt;3,3-K10,"No aplica")</f>
@@ -5029,7 +5031,7 @@
       </c>
       <c r="F11" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G11" s="1">
         <v>4.75</v>
@@ -5038,18 +5040,20 @@
         <f>G11*0.5</f>
         <v>2.375</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="6">
+        <v>8</v>
+      </c>
       <c r="J11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="K11" s="6">
         <f t="shared" si="2"/>
-        <v>4.7750000000000004</v>
+        <v>4.6790000000000003</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>4.7799999999999994</v>
       </c>
       <c r="M11" s="1" t="str">
         <f>IF(K11&lt;3,3-K11,"No aplica")</f>
@@ -5070,7 +5074,7 @@
       </c>
       <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G12" s="1">
         <v>4.2</v>
@@ -5084,15 +5088,15 @@
       </c>
       <c r="J12" s="6">
         <f t="shared" si="1"/>
-        <v>1.6E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="K12" s="6">
         <f t="shared" si="2"/>
-        <v>4.516</v>
+        <v>4.4039999999999999</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="M12" s="1" t="str">
         <f>IF(K12&lt;3,3-K12,"No aplica")</f>
@@ -5113,7 +5117,7 @@
       </c>
       <c r="F13" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G13" s="1">
         <v>4.5</v>
@@ -5123,19 +5127,19 @@
         <v>2.25</v>
       </c>
       <c r="I13" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="1"/>
-        <v>1.6E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="2"/>
-        <v>4.766</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="L13" s="6">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>4.7999999999999989</v>
       </c>
       <c r="M13" s="1" t="str">
         <f>IF(K13&lt;3,3-K13,"No aplica")</f>
@@ -5156,7 +5160,7 @@
       </c>
       <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -5170,15 +5174,15 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="1"/>
-        <v>1.8000000000000002E-2</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="2"/>
-        <v>4.5179999999999998</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="M14" s="1" t="str">
         <f>IF(K14&lt;3,3-K14,"No aplica")</f>
@@ -5199,7 +5203,7 @@
       </c>
       <c r="F15" s="5">
         <f t="shared" si="0"/>
-        <v>2.35</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="G15" s="1">
         <v>4.5999999999999996</v>
@@ -5213,15 +5217,15 @@
       </c>
       <c r="J15" s="6">
         <f t="shared" si="1"/>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="2"/>
-        <v>4.66</v>
+        <v>4.5559999999999992</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="3"/>
-        <v>4.6999999999999993</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="M15" s="1" t="str">
         <f>IF(K15&lt;3,3-K15,"No aplica")</f>
@@ -5242,7 +5246,7 @@
       </c>
       <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G16" s="1">
         <v>4.5</v>
@@ -5252,19 +5256,19 @@
         <v>2.25</v>
       </c>
       <c r="I16" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="1"/>
-        <v>1.6E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="2"/>
-        <v>4.766</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>4.7999999999999989</v>
       </c>
       <c r="M16" s="1" t="str">
         <f>IF(K16&lt;3,3-K16,"No aplica")</f>
@@ -5281,11 +5285,11 @@
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="G17" s="1">
         <v>5</v>
@@ -5299,19 +5303,19 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="1"/>
-        <v>1.3999999999999999E-2</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="K17" s="6">
         <f t="shared" si="2"/>
-        <v>2.5139999999999998</v>
+        <v>3.46</v>
       </c>
       <c r="L17" s="6">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="M17" s="1">
+        <v>3.57</v>
+      </c>
+      <c r="M17" s="1" t="str">
         <f>IF(K17&lt;3,3-K17,"No aplica")</f>
-        <v>0.48600000000000021</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5328,7 +5332,7 @@
       </c>
       <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G18" s="1">
         <v>4.2</v>
@@ -5342,15 +5346,15 @@
       </c>
       <c r="J18" s="6">
         <f t="shared" si="1"/>
-        <v>1.3999999999999999E-2</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="K18" s="6">
         <f t="shared" si="2"/>
-        <v>4.6139999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="L18" s="6">
         <f t="shared" si="3"/>
-        <v>4.5999999999999996</v>
+        <v>4.57</v>
       </c>
       <c r="M18" s="1" t="str">
         <f>IF(K18&lt;3,3-K18,"No aplica")</f>
@@ -5371,7 +5375,7 @@
       </c>
       <c r="F19" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G19" s="1">
         <v>4.2</v>
@@ -5385,15 +5389,15 @@
       </c>
       <c r="J19" s="6">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002E-2</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="K19" s="6">
         <f t="shared" si="2"/>
-        <v>4.5220000000000002</v>
+        <v>4.4039999999999999</v>
       </c>
       <c r="L19" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.5100000000000007</v>
       </c>
       <c r="M19" s="1" t="str">
         <f>IF(K19&lt;3,3-K19,"No aplica")</f>
@@ -5414,7 +5418,7 @@
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G20" s="1">
         <v>4.2</v>
@@ -5428,15 +5432,15 @@
       </c>
       <c r="J20" s="6">
         <f t="shared" si="1"/>
-        <v>1.8000000000000002E-2</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="K20" s="6">
         <f t="shared" si="2"/>
-        <v>4.6179999999999994</v>
+        <v>4.5</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="3"/>
-        <v>4.5999999999999996</v>
+        <v>4.59</v>
       </c>
       <c r="M20" s="1" t="str">
         <f>IF(K20&lt;3,3-K20,"No aplica")</f>
@@ -5457,7 +5461,7 @@
       </c>
       <c r="F21" s="5">
         <f t="shared" si="0"/>
-        <v>2.35</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="G21" s="1">
         <v>5</v>
@@ -5471,11 +5475,11 @@
       </c>
       <c r="J21" s="6">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="2"/>
-        <v>4.8699999999999992</v>
+        <v>4.7560000000000002</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="3"/>
@@ -5539,7 +5543,7 @@
       </c>
       <c r="F23" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G23" s="1">
         <v>3.4</v>
@@ -5553,15 +5557,15 @@
       </c>
       <c r="J23" s="6">
         <f t="shared" si="1"/>
-        <v>1.8000000000000002E-2</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="K23" s="6">
         <f t="shared" si="2"/>
-        <v>4.1179999999999994</v>
+        <v>4.0039999999999996</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="3"/>
-        <v>4.0999999999999996</v>
+        <v>4.09</v>
       </c>
       <c r="M23" s="1" t="str">
         <f>IF(K23&lt;3,3-K23,"No aplica")</f>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="F24" s="5">
         <f t="shared" si="0"/>
-        <v>2.4500000000000002</v>
+        <v>2.3519999999999999</v>
       </c>
       <c r="G24" s="1">
         <v>2.7</v>
@@ -5596,15 +5600,15 @@
       </c>
       <c r="J24" s="6">
         <f t="shared" si="1"/>
-        <v>1.2E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="2"/>
-        <v>3.8120000000000003</v>
+        <v>3.702</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="3"/>
-        <v>3.8</v>
+        <v>3.7600000000000002</v>
       </c>
       <c r="M24" s="1" t="str">
         <f>IF(K24&lt;3,3-K24,"No aplica")</f>
@@ -5625,7 +5629,7 @@
       </c>
       <c r="F25" s="5">
         <f t="shared" si="0"/>
-        <v>2.15</v>
+        <v>2.0640000000000001</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -5641,11 +5645,11 @@
       </c>
       <c r="K25" s="6">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>4.5640000000000001</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="3"/>
-        <v>4.6999999999999993</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="M25" s="1" t="str">
         <f>IF(K25&lt;3,3-K25,"No aplica")</f>
@@ -5666,7 +5670,7 @@
       </c>
       <c r="F26" s="5">
         <f t="shared" si="0"/>
-        <v>2.2000000000000002</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="G26" s="1">
         <v>4.75</v>
@@ -5682,11 +5686,11 @@
       </c>
       <c r="K26" s="6">
         <f t="shared" si="2"/>
-        <v>4.5750000000000002</v>
+        <v>4.4870000000000001</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="3"/>
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="M26" s="1" t="str">
         <f>IF(K26&lt;3,3-K26,"No aplica")</f>
@@ -5707,7 +5711,7 @@
       </c>
       <c r="F27" s="5">
         <f t="shared" si="0"/>
-        <v>2.4500000000000002</v>
+        <v>2.3519999999999999</v>
       </c>
       <c r="G27" s="1">
         <v>4.4000000000000004</v>
@@ -5721,11 +5725,11 @@
       </c>
       <c r="J27" s="6">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K27" s="6">
         <f t="shared" si="2"/>
-        <v>4.67</v>
+        <v>4.5519999999999996</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="3"/>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="F28" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G28" s="1">
         <v>4</v>
@@ -5764,15 +5768,15 @@
       </c>
       <c r="J28" s="6">
         <f t="shared" si="1"/>
-        <v>1.6E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="K28" s="6">
         <f t="shared" si="2"/>
-        <v>4.516</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="M28" s="1" t="str">
         <f>IF(K28&lt;3,3-K28,"No aplica")</f>
@@ -5793,7 +5797,7 @@
       </c>
       <c r="F29" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G29" s="1">
         <v>4.4000000000000004</v>
@@ -5807,15 +5811,15 @@
       </c>
       <c r="J29" s="6">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K29" s="6">
         <f t="shared" si="2"/>
-        <v>4.72</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L29" s="6">
         <f t="shared" si="3"/>
-        <v>4.7</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="M29" s="1" t="str">
         <f>IF(K29&lt;3,3-K29,"No aplica")</f>
@@ -5836,7 +5840,7 @@
       </c>
       <c r="F30" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G30" s="1">
         <v>4.5</v>
@@ -5850,15 +5854,15 @@
       </c>
       <c r="J30" s="6">
         <f t="shared" si="1"/>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K30" s="6">
         <f t="shared" si="2"/>
-        <v>4.66</v>
+        <v>4.5540000000000003</v>
       </c>
       <c r="L30" s="6">
         <f t="shared" si="3"/>
-        <v>4.6999999999999993</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="M30" s="1" t="str">
         <f>IF(K30&lt;3,3-K30,"No aplica")</f>
@@ -5879,7 +5883,7 @@
       </c>
       <c r="F31" s="5">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="G31" s="1">
         <v>2.1</v>
@@ -5895,11 +5899,11 @@
       </c>
       <c r="K31" s="6">
         <f t="shared" si="2"/>
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="L31" s="6">
         <f t="shared" si="3"/>
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M31" s="1" t="str">
         <f>IF(K31&lt;3,3-K31,"No aplica")</f>
@@ -5920,7 +5924,7 @@
       </c>
       <c r="F32" s="5">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="6">
@@ -5934,15 +5938,15 @@
       </c>
       <c r="K32" s="6">
         <f t="shared" si="2"/>
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="L32" s="6">
         <f t="shared" si="3"/>
-        <v>2.3000000000000003</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M32" s="1">
         <f>IF(K32&lt;3,3-K32,"No aplica")</f>
-        <v>0.75</v>
+        <v>0.83999999999999986</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -5959,7 +5963,7 @@
       </c>
       <c r="F33" s="5">
         <f t="shared" si="0"/>
-        <v>2.4500000000000002</v>
+        <v>2.3519999999999999</v>
       </c>
       <c r="G33" s="1">
         <v>2.7</v>
@@ -5973,15 +5977,15 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" si="1"/>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K33" s="6">
         <f t="shared" si="2"/>
-        <v>3.81</v>
+        <v>3.702</v>
       </c>
       <c r="L33" s="6">
         <f t="shared" si="3"/>
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="M33" s="1" t="str">
         <f>IF(K33&lt;3,3-K33,"No aplica")</f>
@@ -6002,7 +6006,7 @@
       </c>
       <c r="F34" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -6016,15 +6020,15 @@
       </c>
       <c r="J34" s="6">
         <f t="shared" si="1"/>
-        <v>1.2E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K34" s="6">
         <f t="shared" si="2"/>
-        <v>4.5119999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="M34" s="1" t="str">
         <f>IF(K34&lt;3,3-K34,"No aplica")</f>
@@ -6045,7 +6049,7 @@
       </c>
       <c r="F35" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G35" s="1">
         <v>4.5</v>
@@ -6059,11 +6063,11 @@
       </c>
       <c r="J35" s="6">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K35" s="6">
         <f t="shared" si="2"/>
-        <v>4.67</v>
+        <v>4.5540000000000003</v>
       </c>
       <c r="L35" s="6">
         <f t="shared" si="3"/>
@@ -6088,7 +6092,7 @@
       </c>
       <c r="F36" s="5">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G36" s="1">
         <v>4</v>
@@ -6097,18 +6101,20 @@
         <f>G36*0.5</f>
         <v>2</v>
       </c>
-      <c r="I36" s="6"/>
+      <c r="I36" s="6">
+        <v>5</v>
+      </c>
       <c r="J36" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K36" s="6">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L36" s="6">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="M36" s="1" t="str">
         <f>IF(K36&lt;3,3-K36,"No aplica")</f>
@@ -6129,7 +6135,7 @@
       </c>
       <c r="F37" s="5">
         <f t="shared" si="0"/>
-        <v>2.35</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="G37" s="1">
         <v>4.5999999999999996</v>
@@ -6143,15 +6149,15 @@
       </c>
       <c r="J37" s="6">
         <f t="shared" si="1"/>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K37" s="6">
         <f t="shared" si="2"/>
-        <v>4.66</v>
+        <v>4.5559999999999992</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="3"/>
-        <v>4.6999999999999993</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="M37" s="1" t="str">
         <f>IF(K37&lt;3,3-K37,"No aplica")</f>
@@ -6172,7 +6178,7 @@
       </c>
       <c r="F38" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G38" s="1">
         <v>3.4</v>
@@ -6186,15 +6192,15 @@
       </c>
       <c r="J38" s="6">
         <f t="shared" si="1"/>
-        <v>1.2E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K38" s="6">
         <f t="shared" si="2"/>
-        <v>4.1119999999999992</v>
+        <v>4.0039999999999996</v>
       </c>
       <c r="L38" s="6">
         <f t="shared" si="3"/>
-        <v>4.0999999999999996</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="M38" s="1" t="str">
         <f>IF(K38&lt;3,3-K38,"No aplica")</f>
@@ -6215,7 +6221,7 @@
       </c>
       <c r="F39" s="5">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.3039999999999998</v>
       </c>
       <c r="G39" s="1">
         <v>4.75</v>
@@ -6229,15 +6235,15 @@
       </c>
       <c r="J39" s="6">
         <f t="shared" si="1"/>
-        <v>1.6E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="K39" s="6">
         <f t="shared" si="2"/>
-        <v>4.7910000000000004</v>
+        <v>4.6790000000000003</v>
       </c>
       <c r="L39" s="6">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>4.7799999999999994</v>
       </c>
       <c r="M39" s="1" t="str">
         <f>IF(K39&lt;3,3-K39,"No aplica")</f>

--- a/Corte_2.xlsx
+++ b/Corte_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2698" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0ECA88A-A865-43F9-B6CC-24EF1CADB1E8}"/>
+  <xr:revisionPtr revIDLastSave="2708" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA166873-0489-43A2-B0CC-186F90E79490}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,13 +599,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -623,21 +635,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -652,6 +649,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1287,49 +1287,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="44"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
@@ -1338,40 +1338,40 @@
       <c r="S3" s="12"/>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.2</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="43"/>
       <c r="L6" s="3">
         <v>0.3</v>
       </c>
@@ -1381,13 +1381,13 @@
       <c r="N6" s="4">
         <v>0.5</v>
       </c>
-      <c r="O6" s="40" t="s">
+      <c r="O6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="42"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="41"/>
       <c r="T6" s="11" t="s">
         <v>13</v>
       </c>
@@ -1402,14 +1402,14 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="32"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="33"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5">
         <f>E39*0.1</f>
@@ -3061,13 +3061,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="15">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -3076,6 +3069,13 @@
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E39">
     <cfRule type="expression" dxfId="26" priority="7">
@@ -3143,66 +3143,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30" t="s">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="30"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="22">
         <v>0.5</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="33"/>
       <c r="E39" s="1">
         <v>4.9000000000000004</v>
       </c>
@@ -4787,58 +4787,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4868,14 +4868,14 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="32"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="23" t="s">
         <v>91</v>
       </c>
@@ -5116,8 +5116,8 @@
         <v>5</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E13:E13)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G13" s="1">
         <v>4.5</v>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="K13" s="6">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="L13" s="6">
         <f t="shared" si="3"/>
-        <v>4.7999999999999989</v>
+        <v>4.8999999999999995</v>
       </c>
       <c r="M13" s="1" t="str">
         <f>IF(K13&lt;3,3-K13,"No aplica")</f>
@@ -5159,8 +5159,8 @@
         <v>5</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E14:E14)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -5178,11 +5178,11 @@
       </c>
       <c r="K14" s="6">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="3"/>
-        <v>4.49</v>
+        <v>4.59</v>
       </c>
       <c r="M14" s="1" t="str">
         <f>IF(K14&lt;3,3-K14,"No aplica")</f>
@@ -5245,8 +5245,8 @@
         <v>5</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E16:E16)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G16" s="1">
         <v>4.5</v>
@@ -5264,11 +5264,11 @@
       </c>
       <c r="K16" s="6">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="3"/>
-        <v>4.7999999999999989</v>
+        <v>4.8999999999999995</v>
       </c>
       <c r="M16" s="1" t="str">
         <f>IF(K16&lt;3,3-K16,"No aplica")</f>
@@ -5331,8 +5331,8 @@
         <v>5</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E18:E18)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G18" s="1">
         <v>4.2</v>
@@ -5350,11 +5350,11 @@
       </c>
       <c r="K18" s="6">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L18" s="6">
         <f t="shared" si="3"/>
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="M18" s="1" t="str">
         <f>IF(K18&lt;3,3-K18,"No aplica")</f>
@@ -5417,8 +5417,8 @@
         <v>5</v>
       </c>
       <c r="F20" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E20:E20)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G20" s="1">
         <v>4.2</v>
@@ -5436,11 +5436,11 @@
       </c>
       <c r="K20" s="6">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="3"/>
-        <v>4.59</v>
+        <v>4.6899999999999995</v>
       </c>
       <c r="M20" s="1" t="str">
         <f>IF(K20&lt;3,3-K20,"No aplica")</f>
@@ -5753,8 +5753,8 @@
         <v>5</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E28:E28)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G28" s="1">
         <v>4</v>
@@ -5772,11 +5772,11 @@
       </c>
       <c r="K28" s="6">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="L28" s="6">
         <f t="shared" si="3"/>
-        <v>4.4800000000000004</v>
+        <v>4.58</v>
       </c>
       <c r="M28" s="1" t="str">
         <f>IF(K28&lt;3,3-K28,"No aplica")</f>
@@ -5788,16 +5788,16 @@
         <v>66</v>
       </c>
       <c r="B29" s="15"/>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="34"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="1">
         <v>5</v>
       </c>
       <c r="F29" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E29:E29)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G29" s="1">
         <v>4.4000000000000004</v>
@@ -5815,11 +5815,11 @@
       </c>
       <c r="K29" s="6">
         <f t="shared" si="2"/>
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L29" s="6">
         <f t="shared" si="3"/>
-        <v>4.6999999999999993</v>
+        <v>4.8</v>
       </c>
       <c r="M29" s="1" t="str">
         <f>IF(K29&lt;3,3-K29,"No aplica")</f>
@@ -6005,8 +6005,8 @@
         <v>5</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E34:E34)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -6024,11 +6024,11 @@
       </c>
       <c r="K34" s="6">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="3"/>
-        <v>4.46</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="M34" s="1" t="str">
         <f>IF(K34&lt;3,3-K34,"No aplica")</f>
@@ -6091,8 +6091,8 @@
         <v>5</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <f>AVERAGE(E36:E36)*0.5</f>
+        <v>2.5</v>
       </c>
       <c r="G36" s="1">
         <v>4</v>
@@ -6110,11 +6110,11 @@
       </c>
       <c r="K36" s="6">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="L36" s="6">
         <f t="shared" si="3"/>
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="M36" s="1" t="str">
         <f>IF(K36&lt;3,3-K36,"No aplica")</f>
@@ -6215,7 +6215,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="33"/>
       <c r="E39" s="1">
         <v>4.8</v>
       </c>
@@ -6252,12 +6252,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A4:B4"/>
@@ -6266,6 +6260,12 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E39">
     <cfRule type="expression" dxfId="7" priority="2">

--- a/Corte_2.xlsx
+++ b/Corte_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2708" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA166873-0489-43A2-B0CC-186F90E79490}"/>
+  <xr:revisionPtr revIDLastSave="2732" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B88D95E9-2172-4204-B895-C548E7ABEEC8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="95">
   <si>
     <t>Asignatura</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>Puntos extra y bonos (0,01 cada uno)</t>
+  </si>
+  <si>
+    <t>Definitiva sin firmas</t>
+  </si>
+  <si>
+    <t>Definitiva con firmas</t>
   </si>
   <si>
     <t>Taller 3</t>
@@ -599,25 +605,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -635,6 +629,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -649,9 +658,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1287,49 +1293,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="44"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="39"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
@@ -1338,40 +1344,40 @@
       <c r="S3" s="12"/>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.2</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="44"/>
       <c r="L6" s="3">
         <v>0.3</v>
       </c>
@@ -1381,13 +1387,13 @@
       <c r="N6" s="4">
         <v>0.5</v>
       </c>
-      <c r="O6" s="39" t="s">
+      <c r="O6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="42"/>
       <c r="T6" s="11" t="s">
         <v>13</v>
       </c>
@@ -1402,14 +1408,14 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -3010,7 +3016,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="33"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5">
         <f>E39*0.1</f>
@@ -3061,6 +3067,13 @@
     </sortState>
   </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -3069,13 +3082,6 @@
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E39">
     <cfRule type="expression" dxfId="26" priority="7">
@@ -3143,66 +3149,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="22">
         <v>0.5</v>
       </c>
@@ -4674,7 +4680,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="33"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="1">
         <v>4.9000000000000004</v>
       </c>
@@ -4775,7 +4781,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF495F52-79DC-4B8C-B7B6-9C07853A9F19}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="23.5703125" customWidth="1"/>
@@ -4783,62 +4789,64 @@
     <col min="5" max="5" width="38.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="27" t="s">
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="29" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="34" t="s">
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4858,39 +4866,43 @@
         <v>13</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="23"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
-      <c r="M7" s="23"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="M7" s="25"/>
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="14" t="s">
         <v>24</v>
       </c>
@@ -4925,15 +4937,19 @@
         <v>3.21</v>
       </c>
       <c r="L8" s="6">
-        <f>INT(K8*10)/10+IF(MOD(K8*10,1)&gt;=0.5,0.1,0)+J8</f>
-        <v>3.25</v>
-      </c>
-      <c r="M8" s="1" t="str">
+        <f>F8+H8+J8</f>
+        <v>3.26</v>
+      </c>
+      <c r="M8" s="6">
+        <f>INT(L8*10)/10+IF(MOD(L8*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="N8" s="1" t="str">
         <f>IF(K8&lt;3,3-K8,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="14" t="s">
         <v>26</v>
       </c>
@@ -4966,15 +4982,19 @@
         <v>4.5640000000000001</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" ref="L9:L39" si="3">INT(K9*10)/10+IF(MOD(K9*10,1)&gt;=0.5,0.1,0)+J9</f>
+        <f t="shared" ref="L9:L39" si="3">F9+H9+J9</f>
+        <v>4.5640000000000001</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" ref="M9:M39" si="4">INT(L9*10)/10+IF(MOD(L9*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="M9" s="1" t="str">
+      <c r="N9" s="1" t="str">
         <f>IF(K9&lt;3,3-K9,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="14" t="s">
         <v>28</v>
       </c>
@@ -5010,14 +5030,18 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="3"/>
-        <v>4.87</v>
-      </c>
-      <c r="M10" s="1" t="str">
+        <v>4.8260000000000005</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" si="4"/>
+        <v>4.8</v>
+      </c>
+      <c r="N10" s="1" t="str">
         <f>IF(K10&lt;3,3-K10,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="14" t="s">
         <v>30</v>
       </c>
@@ -5053,14 +5077,18 @@
       </c>
       <c r="L11" s="6">
         <f t="shared" si="3"/>
-        <v>4.7799999999999994</v>
-      </c>
-      <c r="M11" s="1" t="str">
+        <v>4.7590000000000003</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" si="4"/>
+        <v>4.8</v>
+      </c>
+      <c r="N11" s="1" t="str">
         <f>IF(K11&lt;3,3-K11,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="14" t="s">
         <v>32</v>
       </c>
@@ -5096,14 +5124,18 @@
       </c>
       <c r="L12" s="6">
         <f t="shared" si="3"/>
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="M12" s="1" t="str">
+        <v>4.484</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="N12" s="1" t="str">
         <f>IF(K12&lt;3,3-K12,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="14" t="s">
         <v>34</v>
       </c>
@@ -5139,14 +5171,18 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="3"/>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" si="4"/>
         <v>4.8999999999999995</v>
       </c>
-      <c r="M13" s="1" t="str">
+      <c r="N13" s="1" t="str">
         <f>IF(K13&lt;3,3-K13,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14" s="14" t="s">
         <v>36</v>
       </c>
@@ -5184,12 +5220,16 @@
         <f t="shared" si="3"/>
         <v>4.59</v>
       </c>
-      <c r="M14" s="1" t="str">
+      <c r="M14" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N14" s="1" t="str">
         <f>IF(K14&lt;3,3-K14,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="14" t="s">
         <v>38</v>
       </c>
@@ -5225,14 +5265,18 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="3"/>
-        <v>4.6499999999999995</v>
-      </c>
-      <c r="M15" s="1" t="str">
+        <v>4.605999999999999</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N15" s="1" t="str">
         <f>IF(K15&lt;3,3-K15,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" s="14" t="s">
         <v>40</v>
       </c>
@@ -5268,14 +5312,18 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="3"/>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="M16" s="6">
+        <f t="shared" si="4"/>
         <v>4.8999999999999995</v>
       </c>
-      <c r="M16" s="1" t="str">
+      <c r="N16" s="1" t="str">
         <f>IF(K16&lt;3,3-K16,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
@@ -5311,14 +5359,18 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="3"/>
-        <v>3.57</v>
-      </c>
-      <c r="M17" s="1" t="str">
+        <v>3.53</v>
+      </c>
+      <c r="M17" s="6">
+        <f t="shared" si="4"/>
+        <v>3.5</v>
+      </c>
+      <c r="N17" s="1" t="str">
         <f>IF(K17&lt;3,3-K17,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18" s="14" t="s">
         <v>44</v>
       </c>
@@ -5356,12 +5408,16 @@
         <f t="shared" si="3"/>
         <v>4.67</v>
       </c>
-      <c r="M18" s="1" t="str">
+      <c r="M18" s="6">
+        <f t="shared" si="4"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="N18" s="1" t="str">
         <f>IF(K18&lt;3,3-K18,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="14" t="s">
         <v>46</v>
       </c>
@@ -5397,14 +5453,18 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="3"/>
-        <v>4.5100000000000007</v>
-      </c>
-      <c r="M19" s="1" t="str">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="M19" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="N19" s="1" t="str">
         <f>IF(K19&lt;3,3-K19,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20" s="14" t="s">
         <v>48</v>
       </c>
@@ -5442,12 +5502,16 @@
         <f t="shared" si="3"/>
         <v>4.6899999999999995</v>
       </c>
-      <c r="M20" s="1" t="str">
+      <c r="M20" s="6">
+        <f t="shared" si="4"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="N20" s="1" t="str">
         <f>IF(K20&lt;3,3-K20,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21" s="14" t="s">
         <v>50</v>
       </c>
@@ -5483,14 +5547,18 @@
       </c>
       <c r="L21" s="6">
         <f t="shared" si="3"/>
+        <v>4.8559999999999999</v>
+      </c>
+      <c r="M21" s="6">
+        <f t="shared" si="4"/>
         <v>4.8999999999999995</v>
       </c>
-      <c r="M21" s="1" t="str">
+      <c r="N21" s="1" t="str">
         <f>IF(K21&lt;3,3-K21,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22" s="14" t="s">
         <v>52</v>
       </c>
@@ -5524,12 +5592,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
         <f>IF(K22&lt;3,3-K22,"No aplica")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23" s="14" t="s">
         <v>54</v>
       </c>
@@ -5565,14 +5637,18 @@
       </c>
       <c r="L23" s="6">
         <f t="shared" si="3"/>
-        <v>4.09</v>
-      </c>
-      <c r="M23" s="1" t="str">
+        <v>4.0939999999999994</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="4"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N23" s="1" t="str">
         <f>IF(K23&lt;3,3-K23,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24" s="14" t="s">
         <v>56</v>
       </c>
@@ -5608,14 +5684,18 @@
       </c>
       <c r="L24" s="6">
         <f t="shared" si="3"/>
-        <v>3.7600000000000002</v>
-      </c>
-      <c r="M24" s="1" t="str">
+        <v>3.762</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="4"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="N24" s="1" t="str">
         <f>IF(K24&lt;3,3-K24,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25" s="14" t="s">
         <v>58</v>
       </c>
@@ -5649,14 +5729,18 @@
       </c>
       <c r="L25" s="6">
         <f t="shared" si="3"/>
+        <v>4.5640000000000001</v>
+      </c>
+      <c r="M25" s="6">
+        <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
-      <c r="M25" s="1" t="str">
+      <c r="N25" s="1" t="str">
         <f>IF(K25&lt;3,3-K25,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:14">
       <c r="A26" s="14" t="s">
         <v>60</v>
       </c>
@@ -5690,14 +5774,18 @@
       </c>
       <c r="L26" s="6">
         <f t="shared" si="3"/>
+        <v>4.4870000000000001</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="4"/>
         <v>4.5</v>
       </c>
-      <c r="M26" s="1" t="str">
+      <c r="N26" s="1" t="str">
         <f>IF(K26&lt;3,3-K26,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:14">
       <c r="A27" s="14" t="s">
         <v>62</v>
       </c>
@@ -5733,14 +5821,18 @@
       </c>
       <c r="L27" s="6">
         <f t="shared" si="3"/>
+        <v>4.6519999999999992</v>
+      </c>
+      <c r="M27" s="6">
+        <f t="shared" si="4"/>
         <v>4.6999999999999993</v>
       </c>
-      <c r="M27" s="1" t="str">
+      <c r="N27" s="1" t="str">
         <f>IF(K27&lt;3,3-K27,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28" s="14" t="s">
         <v>64</v>
       </c>
@@ -5778,20 +5870,24 @@
         <f t="shared" si="3"/>
         <v>4.58</v>
       </c>
-      <c r="M28" s="1" t="str">
+      <c r="M28" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N28" s="1" t="str">
         <f>IF(K28&lt;3,3-K28,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:14">
       <c r="A29" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B29" s="15"/>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="1">
         <v>5</v>
       </c>
@@ -5821,12 +5917,16 @@
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
-      <c r="M29" s="1" t="str">
+      <c r="M29" s="6">
+        <f t="shared" si="4"/>
+        <v>4.8</v>
+      </c>
+      <c r="N29" s="1" t="str">
         <f>IF(K29&lt;3,3-K29,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:14">
       <c r="A30" s="14" t="s">
         <v>68</v>
       </c>
@@ -5862,14 +5962,18 @@
       </c>
       <c r="L30" s="6">
         <f t="shared" si="3"/>
-        <v>4.6499999999999995</v>
-      </c>
-      <c r="M30" s="1" t="str">
+        <v>4.6040000000000001</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N30" s="1" t="str">
         <f>IF(K30&lt;3,3-K30,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:14">
       <c r="A31" s="14" t="s">
         <v>70</v>
       </c>
@@ -5903,14 +6007,18 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="3"/>
+        <v>3.21</v>
+      </c>
+      <c r="M31" s="6">
+        <f t="shared" si="4"/>
         <v>3.2</v>
       </c>
-      <c r="M31" s="1" t="str">
+      <c r="N31" s="1" t="str">
         <f>IF(K31&lt;3,3-K31,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:14">
       <c r="A32" s="14" t="s">
         <v>72</v>
       </c>
@@ -5942,14 +6050,18 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="3"/>
+        <v>2.16</v>
+      </c>
+      <c r="M32" s="6">
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M32" s="1">
+      <c r="N32" s="1">
         <f>IF(K32&lt;3,3-K32,"No aplica")</f>
         <v>0.83999999999999986</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:14">
       <c r="A33" s="20">
         <v>1011098258</v>
       </c>
@@ -5985,14 +6097,18 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="3"/>
-        <v>3.75</v>
-      </c>
-      <c r="M33" s="1" t="str">
+        <v>3.7519999999999998</v>
+      </c>
+      <c r="M33" s="6">
+        <f t="shared" si="4"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="N33" s="1" t="str">
         <f>IF(K33&lt;3,3-K33,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:14">
       <c r="A34" s="14" t="s">
         <v>75</v>
       </c>
@@ -6030,12 +6146,16 @@
         <f t="shared" si="3"/>
         <v>4.5599999999999996</v>
       </c>
-      <c r="M34" s="1" t="str">
+      <c r="M34" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N34" s="1" t="str">
         <f>IF(K34&lt;3,3-K34,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:14">
       <c r="A35" s="14" t="s">
         <v>77</v>
       </c>
@@ -6071,14 +6191,18 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="3"/>
+        <v>4.6539999999999999</v>
+      </c>
+      <c r="M35" s="6">
+        <f t="shared" si="4"/>
         <v>4.6999999999999993</v>
       </c>
-      <c r="M35" s="1" t="str">
+      <c r="N35" s="1" t="str">
         <f>IF(K35&lt;3,3-K35,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:14">
       <c r="A36" s="14" t="s">
         <v>79</v>
       </c>
@@ -6116,12 +6240,16 @@
         <f t="shared" si="3"/>
         <v>4.55</v>
       </c>
-      <c r="M36" s="1" t="str">
+      <c r="M36" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N36" s="1" t="str">
         <f>IF(K36&lt;3,3-K36,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:14">
       <c r="A37" s="14" t="s">
         <v>81</v>
       </c>
@@ -6157,14 +6285,18 @@
       </c>
       <c r="L37" s="6">
         <f t="shared" si="3"/>
-        <v>4.6499999999999995</v>
-      </c>
-      <c r="M37" s="1" t="str">
+        <v>4.605999999999999</v>
+      </c>
+      <c r="M37" s="6">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N37" s="1" t="str">
         <f>IF(K37&lt;3,3-K37,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:14">
       <c r="A38" s="17" t="s">
         <v>83</v>
       </c>
@@ -6200,14 +6332,18 @@
       </c>
       <c r="L38" s="6">
         <f t="shared" si="3"/>
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="M38" s="1" t="str">
+        <v>4.0639999999999992</v>
+      </c>
+      <c r="M38" s="6">
+        <f t="shared" si="4"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N38" s="1" t="str">
         <f>IF(K38&lt;3,3-K38,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:14">
       <c r="A39" s="48" t="s">
         <v>85</v>
       </c>
@@ -6215,7 +6351,7 @@
       <c r="C39" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="33"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="1">
         <v>4.8</v>
       </c>
@@ -6243,15 +6379,25 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="3"/>
-        <v>4.7799999999999994</v>
-      </c>
-      <c r="M39" s="1" t="str">
+        <v>4.7590000000000003</v>
+      </c>
+      <c r="M39" s="6">
+        <f t="shared" si="4"/>
+        <v>4.8</v>
+      </c>
+      <c r="N39" s="1" t="str">
         <f>IF(K39&lt;3,3-K39,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A4:B4"/>
@@ -6260,12 +6406,6 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E39">
     <cfRule type="expression" dxfId="7" priority="2">
@@ -6291,7 +6431,7 @@
       <formula>LEN(TRIM(I8))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K39">
+  <conditionalFormatting sqref="K8:L39">
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>K8&gt;=3</formula>
     </cfRule>
